--- a/ig/ch-vacd/StructureDefinition-ch-vacd-document-vaccination-record.xlsx
+++ b/ig/ch-vacd/StructureDefinition-ch-vacd-document-vaccination-record.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T10:03:10+00:00</t>
+    <t>2026-06-11T13:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -749,7 +749,7 @@
     <t>Bundle.entry</t>
   </si>
   <si>
-    <t>3</t>
+    <t>2</t>
   </si>
   <si>
     <t>Entry in the bundle - will have a resource or information</t>
@@ -24213,7 +24213,7 @@
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G185" t="s" s="2">
         <v>80</v>
